--- a/astro-site/public/dl/kit-escandallos/02-menu-degustacion.xlsx
+++ b/astro-site/public/dl/kit-escandallos/02-menu-degustacion.xlsx
@@ -41,7 +41,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'9. Pase'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'9. Pase'!$A$1:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'Resumen'!$A$1:$J$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'Conversiones'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Conversiones'!$A$1:$J$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'Mermas'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1134,256 +1134,263 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
+          <t>▸ ¿Llevas tus precios en la plantilla 13 (Lista de Precios de Ingredientes)? Lleva su «Precio por unidad base» a «Precio/Ud (€)» con Pegado especial → Valores (en Excel, Ctrl+Alt+V y luego V) y pon esa misma unidad en «Ud. Compra». Un pegado normal arrastraría la fórmula: el precio y el coste de esa línea se quedarían en blanco sin avisar, y el coste del plato saldría más bajo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
+          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
+          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
+          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
+          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>▸ Coste (€): Cant. Bruta × Precio/Ud ÷ Factor (automático).</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Bloque de resultado</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
+          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
+          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
+          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
+          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
+          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t>▸ FOOD COST REAL (%): coste por ración ÷ PVP actual. Se pone en rojo en cuanto supera tu objetivo.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Hojas auxiliares</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>▸ «Mermas»: merma mínima, típica y máxima por categoría. La típica es la que se precarga en las filas vacías.</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Protección de la hoja</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
-        </is>
-      </c>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
+          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>▸ La foto del plato NO se puede arrastrar con la hoja protegida: primero Revisar → Desproteger hoja, y después Insertar → Imagen.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Referencia de mermas estándar</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
-        </is>
-      </c>
-    </row>
+    <row r="52"/>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
+          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
+          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
+          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
+          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>▸ Pasta/arroz 2 %</t>
+          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>▸ Pasta/arroz 2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
           <t>▸ Son las 21 categorías del desplegable. La tabla completa, con mínimo y máximo, está en la hoja «Mermas».</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="B62" s="6" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="64"/>
+    <row r="65">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1520,7 @@
       <c r="E5" s="64" t="n"/>
       <c r="F5" s="62" t="n"/>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H5" s="66">
@@ -1539,7 +1546,7 @@
       <c r="E6" s="64" t="n"/>
       <c r="F6" s="62" t="n"/>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H6" s="66">
@@ -1565,7 +1572,7 @@
       <c r="E7" s="64" t="n"/>
       <c r="F7" s="62" t="n"/>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H7" s="66">
@@ -1591,7 +1598,7 @@
       <c r="E8" s="64" t="n"/>
       <c r="F8" s="62" t="n"/>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H8" s="66">
@@ -1623,7 +1630,7 @@
       <c r="E9" s="64" t="n"/>
       <c r="F9" s="62" t="n"/>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H9" s="66">
@@ -1649,7 +1656,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -1675,7 +1682,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -1701,7 +1708,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -1727,7 +1734,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -1753,7 +1760,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -1779,7 +1786,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -1805,7 +1812,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -1831,7 +1838,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -1857,7 +1864,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -1883,7 +1890,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -2153,20 +2160,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -2423,7 +2430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2441,7 +2448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final: la clave se escribe «compra→uso».</t>
+          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final, hasta la fila 67: la clave se escribe «compra→uso».</t>
         </is>
       </c>
     </row>
@@ -2958,6 +2965,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
   </sheetData>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3001,7 +3009,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mide tu merma real con la plantilla 12 (Test de Rendimiento) y llévala a «Merma (%)» de la ficha.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="77" t="inlineStr">
         <is>
@@ -3503,7 +3517,7 @@
         </is>
       </c>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="66" t="n">
@@ -3548,7 +3562,7 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="66" t="n">
@@ -3593,7 +3607,7 @@
         </is>
       </c>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="66" t="n">
@@ -3618,7 +3632,7 @@
       </c>
       <c r="B8" s="62" t="inlineStr">
         <is>
-          <t>Bebidas/licores</t>
+          <t>Salsas/condimentos</t>
         </is>
       </c>
       <c r="C8" s="62" t="inlineStr">
@@ -3638,7 +3652,7 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="66" t="n">
@@ -3689,7 +3703,7 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="66" t="n">
@@ -3714,7 +3728,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -3740,7 +3754,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -3766,7 +3780,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -3792,7 +3806,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -3818,7 +3832,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -3844,7 +3858,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -3870,7 +3884,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -3896,7 +3910,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -3922,7 +3936,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -3948,7 +3962,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -4218,20 +4232,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -4396,7 +4410,7 @@
         </is>
       </c>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="66" t="n">
@@ -4421,7 +4435,7 @@
       </c>
       <c r="B6" s="62" t="inlineStr">
         <is>
-          <t>Verdura raíz</t>
+          <t>Verdura hoja</t>
         </is>
       </c>
       <c r="C6" s="62" t="inlineStr">
@@ -4441,7 +4455,7 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="66" t="n">
@@ -4486,7 +4500,7 @@
         </is>
       </c>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="66" t="n">
@@ -4531,7 +4545,7 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="66" t="n">
@@ -4582,7 +4596,7 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="66" t="n">
@@ -4607,7 +4621,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -4633,7 +4647,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -4659,7 +4673,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -4685,7 +4699,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -4711,7 +4725,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -4737,7 +4751,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -4763,7 +4777,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -4789,7 +4803,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -4815,7 +4829,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -4841,7 +4855,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -5111,20 +5125,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -5289,7 +5303,7 @@
         </is>
       </c>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="66" t="n">
@@ -5334,7 +5348,7 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="66" t="n">
@@ -5379,7 +5393,7 @@
         </is>
       </c>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="66" t="n">
@@ -5424,7 +5438,7 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="66" t="n">
@@ -5455,7 +5469,7 @@
       </c>
       <c r="B9" s="62" t="inlineStr">
         <is>
-          <t>Verdura hoja</t>
+          <t>Verdura raíz</t>
         </is>
       </c>
       <c r="C9" s="62" t="inlineStr">
@@ -5475,7 +5489,7 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="66" t="n">
@@ -5500,7 +5514,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -5526,7 +5540,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -5552,7 +5566,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -5578,7 +5592,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -5604,7 +5618,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -5630,7 +5644,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -5656,7 +5670,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -5682,7 +5696,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -5708,7 +5722,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -5734,7 +5748,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -6004,20 +6018,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -6182,7 +6196,7 @@
         </is>
       </c>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="66" t="n">
@@ -6227,7 +6241,7 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="66" t="n">
@@ -6272,7 +6286,7 @@
         </is>
       </c>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="66" t="n">
@@ -6317,7 +6331,7 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="66" t="n">
@@ -6368,7 +6382,7 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="66" t="n">
@@ -6393,7 +6407,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -6419,7 +6433,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -6445,7 +6459,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -6471,7 +6485,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -6497,7 +6511,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -6523,7 +6537,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -6549,7 +6563,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -6575,7 +6589,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -6601,7 +6615,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -6627,7 +6641,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -6897,20 +6911,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -7075,7 +7089,7 @@
         </is>
       </c>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="66" t="n">
@@ -7120,7 +7134,7 @@
         </is>
       </c>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="66" t="n">
@@ -7165,7 +7179,7 @@
         </is>
       </c>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="66" t="n">
@@ -7210,7 +7224,7 @@
         </is>
       </c>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="66" t="n">
@@ -7261,7 +7275,7 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="66" t="n">
@@ -7286,7 +7300,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -7312,7 +7326,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -7338,7 +7352,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -7364,7 +7378,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -7390,7 +7404,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -7416,7 +7430,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -7442,7 +7456,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -7468,7 +7482,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -7494,7 +7508,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -7520,7 +7534,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -7790,20 +7804,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -7948,7 +7962,7 @@
       <c r="E5" s="64" t="n"/>
       <c r="F5" s="62" t="n"/>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H5" s="66">
@@ -7974,7 +7988,7 @@
       <c r="E6" s="64" t="n"/>
       <c r="F6" s="62" t="n"/>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H6" s="66">
@@ -8000,7 +8014,7 @@
       <c r="E7" s="64" t="n"/>
       <c r="F7" s="62" t="n"/>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H7" s="66">
@@ -8026,7 +8040,7 @@
       <c r="E8" s="64" t="n"/>
       <c r="F8" s="62" t="n"/>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H8" s="66">
@@ -8058,7 +8072,7 @@
       <c r="E9" s="64" t="n"/>
       <c r="F9" s="62" t="n"/>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H9" s="66">
@@ -8084,7 +8098,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -8110,7 +8124,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -8136,7 +8150,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -8162,7 +8176,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -8188,7 +8202,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -8214,7 +8228,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -8240,7 +8254,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -8266,7 +8280,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -8292,7 +8306,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -8318,7 +8332,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -8588,20 +8602,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -8746,7 +8760,7 @@
       <c r="E5" s="64" t="n"/>
       <c r="F5" s="62" t="n"/>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H5" s="66">
@@ -8772,7 +8786,7 @@
       <c r="E6" s="64" t="n"/>
       <c r="F6" s="62" t="n"/>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H6" s="66">
@@ -8798,7 +8812,7 @@
       <c r="E7" s="64" t="n"/>
       <c r="F7" s="62" t="n"/>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H7" s="66">
@@ -8824,7 +8838,7 @@
       <c r="E8" s="64" t="n"/>
       <c r="F8" s="62" t="n"/>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H8" s="66">
@@ -8856,7 +8870,7 @@
       <c r="E9" s="64" t="n"/>
       <c r="F9" s="62" t="n"/>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H9" s="66">
@@ -8882,7 +8896,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -8908,7 +8922,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -8934,7 +8948,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -8960,7 +8974,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -8986,7 +9000,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -9012,7 +9026,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -9038,7 +9052,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -9064,7 +9078,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -9090,7 +9104,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -9116,7 +9130,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -9386,20 +9400,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
@@ -9544,7 +9558,7 @@
       <c r="E5" s="64" t="n"/>
       <c r="F5" s="62" t="n"/>
       <c r="G5" s="65">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H5" s="66">
@@ -9570,7 +9584,7 @@
       <c r="E6" s="64" t="n"/>
       <c r="F6" s="62" t="n"/>
       <c r="G6" s="65">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H6" s="66">
@@ -9596,7 +9610,7 @@
       <c r="E7" s="64" t="n"/>
       <c r="F7" s="62" t="n"/>
       <c r="G7" s="65">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H7" s="66">
@@ -9622,7 +9636,7 @@
       <c r="E8" s="64" t="n"/>
       <c r="F8" s="62" t="n"/>
       <c r="G8" s="65">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H8" s="66">
@@ -9654,7 +9668,7 @@
       <c r="E9" s="64" t="n"/>
       <c r="F9" s="62" t="n"/>
       <c r="G9" s="65">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H9" s="66">
@@ -9680,7 +9694,7 @@
       <c r="E10" s="67" t="n"/>
       <c r="F10" s="67" t="n"/>
       <c r="G10" s="65">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H10" s="68">
@@ -9706,7 +9720,7 @@
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
       <c r="G11" s="65">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="68">
@@ -9732,7 +9746,7 @@
       <c r="E12" s="67" t="n"/>
       <c r="F12" s="67" t="n"/>
       <c r="G12" s="65">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="68">
@@ -9758,7 +9772,7 @@
       <c r="E13" s="67" t="n"/>
       <c r="F13" s="67" t="n"/>
       <c r="G13" s="65">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="68">
@@ -9784,7 +9798,7 @@
       <c r="E14" s="67" t="n"/>
       <c r="F14" s="67" t="n"/>
       <c r="G14" s="65">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="68">
@@ -9810,7 +9824,7 @@
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="65">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="68">
@@ -9836,7 +9850,7 @@
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
       <c r="G16" s="65">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="68">
@@ -9862,7 +9876,7 @@
       <c r="E17" s="67" t="n"/>
       <c r="F17" s="67" t="n"/>
       <c r="G17" s="65">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="68">
@@ -9888,7 +9902,7 @@
       <c r="E18" s="67" t="n"/>
       <c r="F18" s="67" t="n"/>
       <c r="G18" s="65">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="68">
@@ -9914,7 +9928,7 @@
       <c r="E19" s="67" t="n"/>
       <c r="F19" s="67" t="n"/>
       <c r="G19" s="65">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="68">
@@ -10184,20 +10198,20 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A1:J1"/>
